--- a/research/study_002_foundation_model_comparison/analysis/statistical_outputs/anova_results.xlsx
+++ b/research/study_002_foundation_model_comparison/analysis/statistical_outputs/anova_results.xlsx
@@ -1,25 +1,237 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\3-6-2023\muawia 03-06-2026\Agentic-AI-research\research\study_002_foundation_model_comparison\analysis\statistical_outputs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D2C183-E138-4C8F-94DD-D35A840610D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-23148" yWindow="1056" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="Quality_ANOVA" sheetId="2" r:id="rId2"/>
+    <sheet name="Confidence_ANOVA" sheetId="3" r:id="rId3"/>
+    <sheet name="Interaction_Analysis" sheetId="4" r:id="rId4"/>
+    <sheet name="PostHoc" sheetId="5" r:id="rId5"/>
+    <sheet name="ANOVA_Decision" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="67">
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Comparison_Factor</t>
+  </si>
+  <si>
+    <t>group1</t>
+  </si>
+  <si>
+    <t>group2</t>
+  </si>
+  <si>
+    <t>meandiff</t>
+  </si>
+  <si>
+    <t>p-adj</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>upper</t>
+  </si>
+  <si>
+    <t>reject</t>
+  </si>
+  <si>
+    <t>quality_score</t>
+  </si>
+  <si>
+    <t>Provider</t>
+  </si>
+  <si>
+    <t>Anthropic</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>OpenAI</t>
+  </si>
+  <si>
+    <t>Workflow</t>
+  </si>
+  <si>
+    <t>basic_agent</t>
+  </si>
+  <si>
+    <t>planner_executor</t>
+  </si>
+  <si>
+    <t>planner_executor_reviewer</t>
+  </si>
+  <si>
+    <t>Provider × Workflow</t>
+  </si>
+  <si>
+    <t>Anthropic | basic_agent</t>
+  </si>
+  <si>
+    <t>Anthropic | planner_executor</t>
+  </si>
+  <si>
+    <t>Anthropic | planner_executor_reviewer</t>
+  </si>
+  <si>
+    <t>Google | basic_agent</t>
+  </si>
+  <si>
+    <t>Google | planner_executor</t>
+  </si>
+  <si>
+    <t>Google | planner_executor_reviewer</t>
+  </si>
+  <si>
+    <t>OpenAI | basic_agent</t>
+  </si>
+  <si>
+    <t>OpenAI | planner_executor</t>
+  </si>
+  <si>
+    <t>OpenAI | planner_executor_reviewer</t>
+  </si>
+  <si>
+    <t>confidence</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Study 002 AnalysisReady</t>
+  </si>
+  <si>
+    <t>Total Observations</t>
+  </si>
+  <si>
+    <t>Providers</t>
+  </si>
+  <si>
+    <t>Workflows</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>3 × 3 factorial design</t>
+  </si>
+  <si>
+    <t>Cell Size</t>
+  </si>
+  <si>
+    <t>30 observations per provider × workflow group</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Two-Way ANOVA</t>
+  </si>
+  <si>
+    <t>ANOVA Type</t>
+  </si>
+  <si>
+    <t>Type II ANOVA</t>
+  </si>
+  <si>
+    <t>Outcomes</t>
+  </si>
+  <si>
+    <t>quality_score, confidence</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>Partial_Eta_Squared</t>
+  </si>
+  <si>
+    <t>Significant</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Interaction_p_value</t>
+  </si>
+  <si>
+    <t>Interaction_Significant</t>
+  </si>
+  <si>
+    <t>Interpretation</t>
+  </si>
+  <si>
+    <t>Provider effects vary by workflow architecture.</t>
+  </si>
+  <si>
+    <t>No statistically significant provider × workflow interaction detected.</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Not significant</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -49,13 +261,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +324,97 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50A1F36E-10FA-4831-AF92-12DF579404EA}" name="Table1" displayName="Table1" ref="A1:B12" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:B12" xr:uid="{50A1F36E-10FA-4831-AF92-12DF579404EA}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{2C6F0110-3263-43ED-A2A8-DF4C2837A1C1}" name="Item" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{E9B76BE3-6D33-4C39-9812-CAD76B4AD4DB}" name="Value" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A34ABFF-519B-44A0-AE94-AC5B75E24D81}" name="Table2" displayName="Table2" ref="A1:H5" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H5" xr:uid="{2A34ABFF-519B-44A0-AE94-AC5B75E24D81}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{D8A50C00-207A-4C5D-87DB-6C0F60457AF9}" name="Outcome" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{99BAD444-4B54-40CD-A1D1-969099E8DCE6}" name="Source" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{E078E19D-7D4A-4DAE-9F43-7D8759211100}" name="SS" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{95140052-9027-42ED-9D04-E2D31195FEAE}" name="df" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{C1E6788B-BE53-4A0F-82C4-CC31CDB34A20}" name="F" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{D7E935F6-095F-41DE-8D55-09BCEEC1CC67}" name="p_value" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{A4A7BB68-0B40-4063-88D8-CFEFA72D2741}" name="Partial_Eta_Squared" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{12EC0506-2F8D-4528-BFA0-E71B2220BC49}" name="Significant" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DE495B19-44D5-455A-A494-2066022A588C}" name="Table3" displayName="Table3" ref="A1:H5" totalsRowShown="0">
+  <autoFilter ref="A1:H5" xr:uid="{DE495B19-44D5-455A-A494-2066022A588C}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{D34CAD4E-B0C9-42E1-A00C-081F39E1F1C6}" name="Outcome"/>
+    <tableColumn id="2" xr3:uid="{9AC0DF0D-BFA3-49AB-A9DA-AC8B845FA151}" name="Source"/>
+    <tableColumn id="3" xr3:uid="{03742C8E-EECC-4597-9B67-1587ED44E83D}" name="SS"/>
+    <tableColumn id="4" xr3:uid="{BAFD202F-7E3D-4C59-B8E1-35ACB3F0FF76}" name="df"/>
+    <tableColumn id="5" xr3:uid="{B8D3A503-B1F0-47A8-BF03-3D2676513F5F}" name="F"/>
+    <tableColumn id="6" xr3:uid="{0E770BA1-2BAB-490D-B90D-A3CB0A84BB13}" name="p_value"/>
+    <tableColumn id="7" xr3:uid="{BA150E58-6F04-4B7D-88CB-8C686BA74DFE}" name="Partial_Eta_Squared"/>
+    <tableColumn id="8" xr3:uid="{CFE67DCE-BCA4-4F34-9C8D-DA2DFBCA0BAF}" name="Significant"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{21D6E94F-B74D-4E3F-8436-5CF1058EB167}" name="Table4" displayName="Table4" ref="A1:D3" totalsRowShown="0">
+  <autoFilter ref="A1:D3" xr:uid="{21D6E94F-B74D-4E3F-8436-5CF1058EB167}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{54CA8BC5-F772-4BCE-8848-B8E31834C1DF}" name="Outcome"/>
+    <tableColumn id="2" xr3:uid="{D1CF1846-4CC6-4034-A72B-62CC3A5F8326}" name="Interaction_p_value"/>
+    <tableColumn id="3" xr3:uid="{6D7D1004-7A3E-4287-B56B-ABC6E3CE6414}" name="Interaction_Significant"/>
+    <tableColumn id="4" xr3:uid="{FF43EAEC-C934-4326-B045-D338F4C09E99}" name="Interpretation"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4946CB11-3179-46EB-ADB1-0E84EF8B98FD}" name="Table5" displayName="Table5" ref="A1:I49" totalsRowShown="0">
+  <autoFilter ref="A1:I49" xr:uid="{4946CB11-3179-46EB-ADB1-0E84EF8B98FD}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{863C8055-43C5-42F9-AF1E-3F3447AF1359}" name="Outcome"/>
+    <tableColumn id="2" xr3:uid="{187BFFC7-0C02-47B1-B92C-8A22B2171A15}" name="Comparison_Factor"/>
+    <tableColumn id="3" xr3:uid="{5D68D5E6-307E-42C0-AF08-B89981E816EE}" name="group1"/>
+    <tableColumn id="4" xr3:uid="{CFE122E2-44D1-442B-BCDD-01BA965C2162}" name="group2"/>
+    <tableColumn id="5" xr3:uid="{E40C0AF3-3179-4C58-8950-D1F78090EDD6}" name="meandiff"/>
+    <tableColumn id="6" xr3:uid="{3A681825-66A5-4620-9971-75805D9AC3D2}" name="p-adj"/>
+    <tableColumn id="7" xr3:uid="{FE79BD45-1E8D-40E1-83B1-40E35B6665B7}" name="lower"/>
+    <tableColumn id="8" xr3:uid="{956D96BE-95EC-4B52-9279-F343233C9813}" name="upper"/>
+    <tableColumn id="9" xr3:uid="{79D7264A-31F2-46A2-BE3A-2424A5591A90}" name="reject"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8551150B-41F9-4F56-99C1-2E972B837042}" name="Table6" displayName="Table6" ref="A1:F7" totalsRowShown="0">
+  <autoFilter ref="A1:F7" xr:uid="{8551150B-41F9-4F56-99C1-2E972B837042}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{B2A4F394-EBAB-41CC-A25F-83A6FE1A4EED}" name="Outcome"/>
+    <tableColumn id="2" xr3:uid="{13C16C14-FD59-4563-95EE-9144B19D17E3}" name="Effect"/>
+    <tableColumn id="3" xr3:uid="{CA0358D6-20A5-4FAB-BB0E-17EE647D2260}" name="F"/>
+    <tableColumn id="4" xr3:uid="{BCCBA7F3-F7F1-4A9D-8B67-D1B5EE8C3BB4}" name="p_value"/>
+    <tableColumn id="5" xr3:uid="{8D768EFD-797C-4BC5-888D-BD166D642F92}" name="Partial_Eta_Squared"/>
+    <tableColumn id="6" xr3:uid="{006FFCCE-3101-4CF8-A89E-E76A8852C7A8}" name="Decision"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +679,2059 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.15512518518518489</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3.185758184252153</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.2959632058343009E-2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2.3830198725143099E-2</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.6977474074074006</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>14.329423755628429</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1.2455438404225959E-6</v>
+      </c>
+      <c r="G3" s="1">
+        <v>9.8940003930462081E-2</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.45509925925925893</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4.6731167092612846</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1.1681099700705431E-3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>6.6832214140167642E-2</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6.3544799999999997</v>
+      </c>
+      <c r="D5" s="1">
+        <v>261</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>0.28844740740740138</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>12.20852639931822</v>
+      </c>
+      <c r="F2">
+        <v>8.5399828147629862E-6</v>
+      </c>
+      <c r="G2">
+        <v>8.554868239026639E-2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>8.5622962962962013E-2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3.6239889036157971</v>
+      </c>
+      <c r="F3">
+        <v>2.8027128625488899E-2</v>
+      </c>
+      <c r="G3">
+        <v>2.7019692250728311E-2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>9.5548148148148646E-2</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>2.0220360091936631</v>
+      </c>
+      <c r="F4">
+        <v>9.1734546518152466E-2</v>
+      </c>
+      <c r="G4">
+        <v>3.0057600886604991E-2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5">
+        <v>3.083286666666667</v>
+      </c>
+      <c r="D5">
+        <v>261</v>
+      </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="62.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>1.1681099700705431E-3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>9.1734546518152466E-2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="4" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="F2">
+        <v>0.98519999999999996</v>
+      </c>
+      <c r="G2">
+        <v>-5.4800000000000001E-2</v>
+      </c>
+      <c r="H2">
+        <v>6.3E-2</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>5.28E-2</v>
+      </c>
+      <c r="F3">
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="G3">
+        <v>-6.1000000000000004E-3</v>
+      </c>
+      <c r="H3">
+        <v>0.11169999999999999</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4">
+        <v>4.87E-2</v>
+      </c>
+      <c r="F4">
+        <v>0.12770000000000001</v>
+      </c>
+      <c r="G4">
+        <v>-1.0200000000000001E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.1076</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="F5">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="G5">
+        <v>-1.7899999999999999E-2</v>
+      </c>
+      <c r="H5">
+        <v>9.5600000000000004E-2</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>-8.3000000000000004E-2</v>
+      </c>
+      <c r="F6">
+        <v>1.9E-3</v>
+      </c>
+      <c r="G6">
+        <v>-0.13969999999999999</v>
+      </c>
+      <c r="H6">
+        <v>-2.63E-2</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>-0.12189999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>-0.17860000000000001</v>
+      </c>
+      <c r="H7">
+        <v>-6.5100000000000005E-2</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="F8">
+        <v>0.99919999999999998</v>
+      </c>
+      <c r="G8">
+        <v>-9.9400000000000002E-2</v>
+      </c>
+      <c r="H8">
+        <v>0.1527</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>-3.3300000000000003E-2</v>
+      </c>
+      <c r="F9">
+        <v>0.996</v>
+      </c>
+      <c r="G9">
+        <v>-0.15939999999999999</v>
+      </c>
+      <c r="H9">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10">
+        <v>2.87E-2</v>
+      </c>
+      <c r="F10">
+        <v>0.99860000000000004</v>
+      </c>
+      <c r="G10">
+        <v>-9.74E-2</v>
+      </c>
+      <c r="H10">
+        <v>0.1547</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11">
+        <v>0.1193</v>
+      </c>
+      <c r="F11">
+        <v>7.9299999999999995E-2</v>
+      </c>
+      <c r="G11">
+        <v>-6.7000000000000002E-3</v>
+      </c>
+      <c r="H11">
+        <v>0.24540000000000001</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12">
+        <v>-0.14230000000000001</v>
+      </c>
+      <c r="F12">
+        <v>1.41E-2</v>
+      </c>
+      <c r="G12">
+        <v>-0.26840000000000003</v>
+      </c>
+      <c r="H12">
+        <v>-1.6299999999999999E-2</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13">
+        <v>6.5699999999999995E-2</v>
+      </c>
+      <c r="F13">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="G13">
+        <v>-6.0400000000000002E-2</v>
+      </c>
+      <c r="H13">
+        <v>0.19170000000000001</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F14">
+        <v>0.79679999999999995</v>
+      </c>
+      <c r="G14">
+        <v>-6.0999999999999999E-2</v>
+      </c>
+      <c r="H14">
+        <v>0.191</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F15">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="G15">
+        <v>-0.105</v>
+      </c>
+      <c r="H15">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>-0.06</v>
+      </c>
+      <c r="F16">
+        <v>0.85980000000000001</v>
+      </c>
+      <c r="G16">
+        <v>-0.186</v>
+      </c>
+      <c r="H16">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17">
+        <v>2E-3</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>-0.124</v>
+      </c>
+      <c r="H17">
+        <v>0.128</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="F18">
+        <v>0.34589999999999999</v>
+      </c>
+      <c r="G18">
+        <v>-3.3399999999999999E-2</v>
+      </c>
+      <c r="H18">
+        <v>0.21870000000000001</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>-0.16900000000000001</v>
+      </c>
+      <c r="F19">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G19">
+        <v>-0.29499999999999998</v>
+      </c>
+      <c r="H19">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20">
+        <v>3.9E-2</v>
+      </c>
+      <c r="F20">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="G20">
+        <v>-8.6999999999999994E-2</v>
+      </c>
+      <c r="H20">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="F21">
+        <v>0.98960000000000004</v>
+      </c>
+      <c r="G21">
+        <v>-8.77E-2</v>
+      </c>
+      <c r="H21">
+        <v>0.16439999999999999</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22">
+        <v>-5.7000000000000002E-3</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>-0.13170000000000001</v>
+      </c>
+      <c r="H22">
+        <v>0.12039999999999999</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23">
+        <v>6.2E-2</v>
+      </c>
+      <c r="F23">
+        <v>0.83609999999999995</v>
+      </c>
+      <c r="G23">
+        <v>-6.4000000000000001E-2</v>
+      </c>
+      <c r="H23">
+        <v>0.188</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>0.1527</v>
+      </c>
+      <c r="F24">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G24">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="H24">
+        <v>0.2787</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>-0.109</v>
+      </c>
+      <c r="F25">
+        <v>0.151</v>
+      </c>
+      <c r="G25">
+        <v>-0.23499999999999999</v>
+      </c>
+      <c r="H25">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="F26">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="G26">
+        <v>-2.7E-2</v>
+      </c>
+      <c r="H26">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27">
+        <v>9.8299999999999998E-2</v>
+      </c>
+      <c r="F27">
+        <v>0.2666</v>
+      </c>
+      <c r="G27">
+        <v>-2.7699999999999999E-2</v>
+      </c>
+      <c r="H27">
+        <v>0.22439999999999999</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>5.4300000000000001E-2</v>
+      </c>
+      <c r="F28">
+        <v>0.91539999999999999</v>
+      </c>
+      <c r="G28">
+        <v>-7.17E-2</v>
+      </c>
+      <c r="H28">
+        <v>0.1804</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29">
+        <v>9.0700000000000003E-2</v>
+      </c>
+      <c r="F29">
+        <v>0.3765</v>
+      </c>
+      <c r="G29">
+        <v>-3.5400000000000001E-2</v>
+      </c>
+      <c r="H29">
+        <v>0.2167</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>-0.17100000000000001</v>
+      </c>
+      <c r="F30">
+        <v>1E-3</v>
+      </c>
+      <c r="G30">
+        <v>-0.29699999999999999</v>
+      </c>
+      <c r="H30">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="F31">
+        <v>0.99180000000000001</v>
+      </c>
+      <c r="G31">
+        <v>-8.8999999999999996E-2</v>
+      </c>
+      <c r="H31">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32">
+        <v>3.6299999999999999E-2</v>
+      </c>
+      <c r="F32">
+        <v>0.99270000000000003</v>
+      </c>
+      <c r="G32">
+        <v>-8.9700000000000002E-2</v>
+      </c>
+      <c r="H32">
+        <v>0.16239999999999999</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33">
+        <v>-7.7000000000000002E-3</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>-0.13370000000000001</v>
+      </c>
+      <c r="H33">
+        <v>0.11840000000000001</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34">
+        <v>-0.26169999999999999</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>-0.38769999999999999</v>
+      </c>
+      <c r="H34">
+        <v>-0.1356</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35">
+        <v>-5.3699999999999998E-2</v>
+      </c>
+      <c r="F35">
+        <v>0.92090000000000005</v>
+      </c>
+      <c r="G35">
+        <v>-0.1797</v>
+      </c>
+      <c r="H35">
+        <v>7.2400000000000006E-2</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36">
+        <v>-5.4300000000000001E-2</v>
+      </c>
+      <c r="F36">
+        <v>0.91539999999999999</v>
+      </c>
+      <c r="G36">
+        <v>-0.1804</v>
+      </c>
+      <c r="H36">
+        <v>7.17E-2</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37">
+        <v>-9.8299999999999998E-2</v>
+      </c>
+      <c r="F37">
+        <v>0.2666</v>
+      </c>
+      <c r="G37">
+        <v>-0.22439999999999999</v>
+      </c>
+      <c r="H37">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H38">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39">
+        <v>0.20730000000000001</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>8.1299999999999997E-2</v>
+      </c>
+      <c r="H39">
+        <v>0.33339999999999997</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40">
+        <v>0.1633</v>
+      </c>
+      <c r="F40">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G40">
+        <v>3.73E-2</v>
+      </c>
+      <c r="H40">
+        <v>0.28939999999999999</v>
+      </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41">
+        <v>-6.9999999999999999E-4</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>-0.12670000000000001</v>
+      </c>
+      <c r="H41">
+        <v>0.12540000000000001</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42">
+        <v>-4.4699999999999997E-2</v>
+      </c>
+      <c r="F42">
+        <v>0.97260000000000002</v>
+      </c>
+      <c r="G42">
+        <v>-0.17069999999999999</v>
+      </c>
+      <c r="H42">
+        <v>8.14E-2</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43">
+        <v>-4.3999999999999997E-2</v>
+      </c>
+      <c r="F43">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="G43">
+        <v>-0.17</v>
+      </c>
+      <c r="H43">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44">
+        <v>7.7799999999999994E-2</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="H44">
+        <v>0.1166</v>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45">
+        <v>5.5300000000000002E-2</v>
+      </c>
+      <c r="F45">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="G45">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="H45">
+        <v>9.4200000000000006E-2</v>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46">
+        <v>-2.24E-2</v>
+      </c>
+      <c r="F46">
+        <v>0.36259999999999998</v>
+      </c>
+      <c r="G46">
+        <v>-6.13E-2</v>
+      </c>
+      <c r="H46">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47">
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="F47">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="G47">
+        <v>-1.1000000000000001E-3</v>
+      </c>
+      <c r="H47">
+        <v>7.8899999999999998E-2</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="F48">
+        <v>8.1600000000000006E-2</v>
+      </c>
+      <c r="G48">
+        <v>-3.5000000000000001E-3</v>
+      </c>
+      <c r="H48">
+        <v>7.6600000000000001E-2</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49">
+        <v>-2.3E-3</v>
+      </c>
+      <c r="F49">
+        <v>0.98970000000000002</v>
+      </c>
+      <c r="G49">
+        <v>-4.24E-2</v>
+      </c>
+      <c r="H49">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>3.185758184252153</v>
+      </c>
+      <c r="D2">
+        <v>4.2959632058343009E-2</v>
+      </c>
+      <c r="E2">
+        <v>2.3830198725143099E-2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>14.329423755628429</v>
+      </c>
+      <c r="D3">
+        <v>1.2455438404225959E-6</v>
+      </c>
+      <c r="E3">
+        <v>9.8940003930462081E-2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>4.6731167092612846</v>
+      </c>
+      <c r="D4">
+        <v>1.1681099700705431E-3</v>
+      </c>
+      <c r="E4">
+        <v>6.6832214140167642E-2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>12.20852639931822</v>
+      </c>
+      <c r="D5">
+        <v>8.5399828147629862E-6</v>
+      </c>
+      <c r="E5">
+        <v>8.554868239026639E-2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>3.6239889036157971</v>
+      </c>
+      <c r="D6">
+        <v>2.8027128625488899E-2</v>
+      </c>
+      <c r="E6">
+        <v>2.7019692250728311E-2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>2.0220360091936631</v>
+      </c>
+      <c r="D7">
+        <v>9.1734546518152466E-2</v>
+      </c>
+      <c r="E7">
+        <v>3.0057600886604991E-2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/research/study_002_foundation_model_comparison/analysis/statistical_outputs/anova_results.xlsx
+++ b/research/study_002_foundation_model_comparison/analysis/statistical_outputs/anova_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\3-6-2023\muawia 03-06-2026\Agentic-AI-research\research\study_002_foundation_model_comparison\analysis\statistical_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D2C183-E138-4C8F-94DD-D35A840610D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC74EE3-7B57-40B0-81AF-9CF5FD1573AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="1056" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -681,13 +681,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -695,7 +695,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -703,7 +703,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -711,7 +711,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -719,7 +719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
@@ -727,7 +727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
@@ -735,7 +735,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -743,7 +743,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -751,7 +751,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -759,7 +759,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
@@ -767,7 +767,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
@@ -775,7 +775,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>47</v>
       </c>
@@ -794,15 +794,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -828,7 +831,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -854,7 +857,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -880,7 +883,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,7 +909,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -937,15 +940,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -971,7 +974,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -997,7 +1000,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1023,7 +1026,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1049,7 +1052,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1077,15 +1080,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="62.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1102,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1113,7 +1116,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1138,16 +1141,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="4" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="4" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1205,7 +1208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1234,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1263,7 +1266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1292,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1321,7 +1324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1350,7 +1353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1379,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1437,7 +1440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1466,7 +1469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1524,7 +1527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1553,7 +1556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1582,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1640,7 +1643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1669,7 +1672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1698,7 +1701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1727,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1756,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1785,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1814,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1843,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1872,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1901,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1930,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1959,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -1988,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -2017,7 +2020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -2046,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -2075,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -2104,7 +2107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -2191,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2220,7 +2223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -2249,7 +2252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -2278,7 +2281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -2307,7 +2310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -2336,7 +2339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -2365,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -2394,7 +2397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>28</v>
       </c>
@@ -2423,7 +2426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>28</v>
       </c>
@@ -2452,7 +2455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>28</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>28</v>
       </c>
@@ -2510,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -2539,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -2579,16 +2582,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2608,7 +2611,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2628,7 +2631,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2648,7 +2651,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2668,7 +2671,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2688,7 +2691,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -2708,7 +2711,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>28</v>
       </c>
